--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Game\Git\TEngine_main\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C0EB4FF-35EF-4E76-A2D3-9184501D6F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC3D82C-FD01-4ECD-9B53-21B0551C3017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28815" yWindow="15" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -133,6 +133,10 @@
   </si>
   <si>
     <t>chapter.TbChapterInfo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>##</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -589,6 +593,9 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Game\Git\TEngine_main\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC3D82C-FD01-4ECD-9B53-21B0551C3017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05313D09-E7C2-4E72-BFB1-61293E110E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,51 +58,6 @@
     <t>##</t>
   </si>
   <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>记录类名</t>
-  </si>
-  <si>
-    <t>从excel读取定义</t>
-  </si>
-  <si>
-    <t>文件列表</t>
-  </si>
-  <si>
-    <t>表id字段</t>
-  </si>
-  <si>
-    <t>模式</t>
-  </si>
-  <si>
-    <t>分组</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>输出文件名</t>
-  </si>
-  <si>
-    <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
-  </si>
-  <si>
-    <t>可以多个，以逗号','分隔</t>
-  </si>
-  <si>
-    <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
-  </si>
-  <si>
-    <t>取值one|map|list，为空自动为map</t>
-  </si>
-  <si>
-    <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
-  </si>
-  <si>
-    <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
-  </si>
-  <si>
     <t>item.TbItem</t>
   </si>
   <si>
@@ -112,39 +67,484 @@
     <t>item.xlsx</t>
   </si>
   <si>
-    <t>chapterItem.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>chapterInfo.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ChapterItem</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ChapterInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>chapter.TbChapterItem</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>chapter.TbChapterInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>##</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>chapterConfig.xlsx</t>
+  </si>
+  <si>
+    <t>chapterEntity.xlsx</t>
+  </si>
+  <si>
+    <t>ChapterConfig</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChapterEntity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>chapter.TbChapterConfig</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>chapter.TbChapterEntity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>全名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>包含模块和名字</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>记录类名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>excel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>读取定义</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>文件列表</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>表</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>字段</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>模式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分组</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>注释</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>输出文件名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>时取已有定义，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为从</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>excel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>标题头和属性栏读取定义</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可以多个，以逗号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>','</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分隔</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为空的话自动取</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>value_type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中第一个字段</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>多主键联合索引为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>key1+key2,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>多主键独立索引为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>"key1,key2"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>取值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>one|map|list</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，为空自动为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>map</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>取值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>c|s|e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，可以有多个，以逗号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t>','</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分隔。空则表示属于所有分组</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="华文新魏"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>默认为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006100"/>
+        <rFont val="JetBrains Mono ExtraBold"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,19 +560,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="JetBrains Mono ExtraBold"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF006100"/>
+      <name val="JetBrains Mono ExtraBold"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF006100"/>
+      <name val="华文新魏"/>
       <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -210,10 +621,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -493,152 +904,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="15.625" customWidth="1"/>
-    <col min="4" max="4" width="32.375" customWidth="1"/>
-    <col min="5" max="5" width="24.375" customWidth="1"/>
-    <col min="6" max="9" width="18" customWidth="1"/>
+    <col min="1" max="1" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="86.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="145.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="53" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="89.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="55.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>20</v>
+      <c r="B2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>26</v>
+      <c r="D3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="b">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
-        <v>29</v>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="b">
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>30</v>
+      <c r="E6" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="b">
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>31</v>
+      <c r="E7" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
